--- a/95 Файлы/Допуск. КТ/Допуск. КТ. Лифты.xlsx
+++ b/95 Файлы/Допуск. КТ/Допуск. КТ. Лифты.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="K2" s="4"/>
       <c r="L2" s="6">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="M2" s="4"/>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="K3" s="4"/>
       <c r="L3" s="6">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="M3" s="4"/>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="K4" s="13"/>
       <c r="L4" s="6">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="M4" s="13"/>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="K5" s="13"/>
       <c r="L5" s="6">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="M5" s="13"/>
     </row>
